--- a/data/trans_bre/P20-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P20-Habitat-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,28; 6,77</t>
+          <t>2,21; 6,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,28</t>
+          <t>1,3; 7,28</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,3; 4,23</t>
+          <t>-1,09; 4,3</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,3; 1,78</t>
+          <t>-3,2; 1,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>60,71; 365,62</t>
+          <t>61,68; 383,24</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,21; 139,28</t>
+          <t>14,2; 140,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-19,41; 105,91</t>
+          <t>-17,7; 104,37</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,07; 34,76</t>
+          <t>-39,56; 30,68</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,8; 6,21</t>
+          <t>1,68; 6,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,85; 5,6</t>
+          <t>1,0; 5,72</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,77; 5,08</t>
+          <t>0,68; 5,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,59; 5,38</t>
+          <t>0,34; 5,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>39,71; 209,61</t>
+          <t>32,82; 200,53</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,96; 113,51</t>
+          <t>13,63; 118,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>13,63; 141,02</t>
+          <t>12,67; 149,42</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>8,44; 213,28</t>
+          <t>5,77; 209,67</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,01; 5,57</t>
+          <t>0,25; 5,91</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,26; 6,1</t>
+          <t>0,36; 6,54</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 5,08</t>
+          <t>0,38; 5,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,03; 1,33</t>
+          <t>-4,17; 1,4</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-1,79; 133,67</t>
+          <t>0,51; 143,55</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,99; 121,83</t>
+          <t>2,09; 131,07</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,63; 157,13</t>
+          <t>4,44; 156,13</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-61,56; 30,6</t>
+          <t>-63,35; 30,84</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,03; 4,15</t>
+          <t>0,01; 4,01</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,88; 5,49</t>
+          <t>0,6; 5,54</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,59; 6,2</t>
+          <t>1,45; 6,2</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,16; 2,02</t>
+          <t>-2,1; 2,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,28; 111,99</t>
+          <t>0,04; 111,05</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>12,09; 125,2</t>
+          <t>8,26; 124,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>24,95; 142,66</t>
+          <t>22,24; 148,48</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-28,49; 35,26</t>
+          <t>-27,34; 41,29</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,16; 4,51</t>
+          <t>2,26; 4,46</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,98; 4,7</t>
+          <t>2,15; 4,76</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,7; 4,06</t>
+          <t>1,82; 4,23</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,81; 1,87</t>
+          <t>-0,91; 2,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>44,27; 120,95</t>
+          <t>45,69; 120,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>29,09; 87,22</t>
+          <t>32,05; 84,73</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,15; 95,6</t>
+          <t>33,56; 97,41</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-13,47; 41,27</t>
+          <t>-14,87; 46,87</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P20-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P20-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-0,73</t>
+          <t>-0,54</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-10,53%</t>
+          <t>-7,79%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2,21; 6,66</t>
+          <t>2,3; 6,66</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>1,3; 7,28</t>
+          <t>1,09; 7,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 4,3</t>
+          <t>-1,2; 4,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-3,2; 1,76</t>
+          <t>-3,18; 1,86</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>61,68; 383,24</t>
+          <t>61,51; 369,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>14,2; 140,96</t>
+          <t>11,84; 131,34</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-17,7; 104,37</t>
+          <t>-19,67; 95,26</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-39,56; 30,68</t>
+          <t>-37,32; 34,25</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,63</t>
+          <t>1,3</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>66,09%</t>
+          <t>25,02%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,68; 6,16</t>
+          <t>1,67; 5,95</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,0; 5,72</t>
+          <t>0,83; 5,67</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,68; 5,13</t>
+          <t>0,75; 5,06</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0,34; 5,14</t>
+          <t>-0,98; 3,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>32,82; 200,53</t>
+          <t>35,67; 197,36</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,63; 118,58</t>
+          <t>12,05; 110,48</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>12,67; 149,42</t>
+          <t>11,4; 144,62</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>5,77; 209,67</t>
+          <t>-16,34; 84,57</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-0,86</t>
+          <t>1,39</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-17,17%</t>
+          <t>29,29%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,25; 5,91</t>
+          <t>-0,2; 5,55</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,36; 6,54</t>
+          <t>0,7; 6,31</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,38; 5,18</t>
+          <t>0,19; 5,21</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-4,17; 1,4</t>
+          <t>-0,71; 3,64</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,51; 143,55</t>
+          <t>-3,73; 127,13</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,09; 131,07</t>
+          <t>8,64; 128,25</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>4,44; 156,13</t>
+          <t>2,59; 163,32</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-63,35; 30,84</t>
+          <t>-12,41; 106,95</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>0,07</t>
+          <t>0,55</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>8,42%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,01; 4,01</t>
+          <t>0,1; 4,35</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,6; 5,54</t>
+          <t>0,81; 5,57</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>1,45; 6,2</t>
+          <t>1,44; 6,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,1; 2,29</t>
+          <t>-1,36; 2,53</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,04; 111,05</t>
+          <t>1,82; 124,18</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,26; 124,55</t>
+          <t>11,82; 131,03</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>22,24; 148,48</t>
+          <t>20,21; 141,92</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-27,34; 41,29</t>
+          <t>-18,89; 45,22</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>0,49</t>
+          <t>0,77</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>13,17%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>2,26; 4,46</t>
+          <t>2,04; 4,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2,15; 4,76</t>
+          <t>2,08; 4,7</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 4,23</t>
+          <t>1,66; 4,03</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-0,91; 2,02</t>
+          <t>-0,26; 1,81</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>45,69; 120,31</t>
+          <t>44,22; 120,32</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,05; 84,73</t>
+          <t>31,37; 87,04</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>33,56; 97,41</t>
+          <t>30,11; 93,92</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-14,87; 46,87</t>
+          <t>-4,07; 34,6</t>
         </is>
       </c>
     </row>
